--- a/output/pdf_financials_xlsx/GEC.xlsx
+++ b/output/pdf_financials_xlsx/GEC.xlsx
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.989246</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.352897</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.204006</v>
       </c>
     </row>
     <row r="93">
@@ -3612,7 +3612,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>1.989246</v>
       </c>

--- a/output/pdf_financials_xlsx/GEC.xlsx
+++ b/output/pdf_financials_xlsx/GEC.xlsx
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.8435049999999999</v>
+        <v>-0.014943</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.118446</v>
+        <v>0.030155</v>
       </c>
     </row>
     <row r="18">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-8.184262905492167</v>
+        <v>-0.1449872147726089</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-17.0317582199522</v>
+        <v>-4.336091291581469</v>
       </c>
     </row>
     <row r="32">
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.118098</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.101765</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.167902</v>
       </c>
     </row>
     <row r="71">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.757164</v>
+        <v>2.875262</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.152492</v>
+        <v>2.254257</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1.552712</v>
+        <v>1.720614</v>
       </c>
     </row>
     <row r="72">
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>18.717557</v>
+        <v>18.599459</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>15.129937</v>
+        <v>15.028172</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>18.601922</v>
+        <v>18.43402</v>
       </c>
     </row>
     <row r="76">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.1017382572448263</v>
+        <v>0.1060387462780658</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1194902613527754</v>
+        <v>0.1250510575239269</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.09262969166606297</v>
+        <v>0.1024468841543572</v>
       </c>
     </row>
     <row r="81">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.059896</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.178564</v>
       </c>
     </row>
     <row r="108">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-1.297004</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.76855</v>
       </c>
     </row>
     <row r="117">
@@ -3345,7 +3345,11 @@
           <t>Current portion of finance lease obligations (Note 12)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.118098</v>
       </c>
@@ -3914,7 +3918,11 @@
           <t>- share-based payment expense</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4307,7 +4315,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -5512,7 +5524,11 @@
           <t>Current income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -5541,7 +5557,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
